--- a/Test Cases for Aarong.xlsx
+++ b/Test Cases for Aarong.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bebed286a0b7e287/Documents/NEW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{2B77E1C0-2E6C-4DBF-BCF0-3144EFCC80D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6AF75D0-38BB-4D19-A363-00F339D9DDE3}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{2B77E1C0-2E6C-4DBF-BCF0-3144EFCC80D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2225ED80-588F-439E-AA53-9B0E37F1563C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sign up" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="254">
   <si>
     <t xml:space="preserve">                                                                                                          Aarong Sign up</t>
   </si>
@@ -943,6 +943,9 @@
   </si>
   <si>
     <t>Embed Link</t>
+  </si>
+  <si>
+    <t>JIRA link</t>
   </si>
 </sst>
 </file>
@@ -1238,6 +1241,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1264,12 +1273,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1440,6 +1443,55 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62A7E5D2-204B-DD89-56F0-7E5662C6EE6F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="47625"/>
+          <a:ext cx="7086600" cy="2952750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1663,18 +1715,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -1772,7 +1824,7 @@
       <c r="AA3" s="5"/>
     </row>
     <row r="4" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="23" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="6"/>
@@ -1802,8 +1854,8 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="24"/>
+      <c r="B5" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="7" t="s">
@@ -1832,8 +1884,8 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="22"/>
-      <c r="B6" s="22"/>
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="7" t="s">
         <v>25</v>
       </c>
@@ -1860,8 +1912,8 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="22"/>
-      <c r="B7" s="23"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="25"/>
       <c r="C7" s="7" t="s">
         <v>29</v>
       </c>
@@ -1888,8 +1940,8 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="22"/>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="24"/>
+      <c r="B8" s="23" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="7" t="s">
@@ -1918,8 +1970,8 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="22"/>
-      <c r="B9" s="22"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="7" t="s">
         <v>37</v>
       </c>
@@ -1946,8 +1998,8 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="22"/>
-      <c r="B10" s="23"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="25"/>
       <c r="C10" s="7" t="s">
         <v>41</v>
       </c>
@@ -1974,8 +2026,8 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="22"/>
-      <c r="B11" s="21" t="s">
+      <c r="A11" s="24"/>
+      <c r="B11" s="23" t="s">
         <v>44</v>
       </c>
       <c r="C11" s="7" t="s">
@@ -2021,8 +2073,8 @@
       <c r="AA11" s="9"/>
     </row>
     <row r="12" spans="1:27" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="22"/>
-      <c r="B12" s="22"/>
+      <c r="A12" s="24"/>
+      <c r="B12" s="24"/>
       <c r="C12" s="7" t="s">
         <v>48</v>
       </c>
@@ -2049,8 +2101,8 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="22"/>
-      <c r="B13" s="22"/>
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
       <c r="C13" s="7" t="s">
         <v>52</v>
       </c>
@@ -2069,7 +2121,7 @@
       <c r="H13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="I13" s="33" t="s">
+      <c r="I13" s="21" t="s">
         <v>56</v>
       </c>
       <c r="J13" s="7" t="s">
@@ -2077,8 +2129,8 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="22"/>
-      <c r="B14" s="23"/>
+      <c r="A14" s="24"/>
+      <c r="B14" s="25"/>
       <c r="C14" s="7" t="s">
         <v>57</v>
       </c>
@@ -2105,8 +2157,8 @@
       </c>
     </row>
     <row r="15" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="22"/>
-      <c r="B15" s="21" t="s">
+      <c r="A15" s="24"/>
+      <c r="B15" s="23" t="s">
         <v>60</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -2135,8 +2187,8 @@
       </c>
     </row>
     <row r="16" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="7" t="s">
         <v>65</v>
       </c>
@@ -2163,8 +2215,8 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="7" t="s">
         <v>68</v>
       </c>
@@ -2191,8 +2243,8 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="22"/>
-      <c r="B18" s="23"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="7" t="s">
         <v>72</v>
       </c>
@@ -2219,8 +2271,8 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="22"/>
-      <c r="B19" s="21" t="s">
+      <c r="A19" s="24"/>
+      <c r="B19" s="23" t="s">
         <v>75</v>
       </c>
       <c r="C19" s="7" t="s">
@@ -2249,8 +2301,8 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
+      <c r="A20" s="24"/>
+      <c r="B20" s="24"/>
       <c r="C20" s="7" t="s">
         <v>79</v>
       </c>
@@ -2277,8 +2329,8 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="22"/>
-      <c r="B21" s="23"/>
+      <c r="A21" s="24"/>
+      <c r="B21" s="25"/>
       <c r="C21" s="7" t="s">
         <v>84</v>
       </c>
@@ -2305,8 +2357,8 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A22" s="22"/>
-      <c r="B22" s="21" t="s">
+      <c r="A22" s="24"/>
+      <c r="B22" s="23" t="s">
         <v>87</v>
       </c>
       <c r="C22" s="7" t="s">
@@ -2335,8 +2387,8 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
+      <c r="A23" s="24"/>
+      <c r="B23" s="24"/>
       <c r="C23" s="7" t="s">
         <v>91</v>
       </c>
@@ -2361,8 +2413,8 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
       <c r="C24" s="7" t="s">
         <v>95</v>
       </c>
@@ -2389,8 +2441,8 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="22"/>
-      <c r="B25" s="22"/>
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
       <c r="C25" s="7" t="s">
         <v>99</v>
       </c>
@@ -2417,8 +2469,8 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A26" s="22"/>
-      <c r="B26" s="23"/>
+      <c r="A26" s="24"/>
+      <c r="B26" s="25"/>
       <c r="C26" s="7" t="s">
         <v>103</v>
       </c>
@@ -2445,8 +2497,8 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="22"/>
-      <c r="B27" s="21" t="s">
+      <c r="A27" s="24"/>
+      <c r="B27" s="23" t="s">
         <v>108</v>
       </c>
       <c r="C27" s="7" t="s">
@@ -2475,8 +2527,8 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
+      <c r="A28" s="24"/>
+      <c r="B28" s="24"/>
       <c r="C28" s="7" t="s">
         <v>112</v>
       </c>
@@ -2503,8 +2555,8 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
       <c r="C29" s="7" t="s">
         <v>115</v>
       </c>
@@ -2529,8 +2581,8 @@
       <c r="J29" s="7"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="22"/>
-      <c r="B30" s="22"/>
+      <c r="A30" s="24"/>
+      <c r="B30" s="24"/>
       <c r="C30" s="7" t="s">
         <v>119</v>
       </c>
@@ -2555,8 +2607,8 @@
       <c r="J30" s="7"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="22"/>
-      <c r="B31" s="23"/>
+      <c r="A31" s="24"/>
+      <c r="B31" s="25"/>
       <c r="C31" s="7" t="s">
         <v>123</v>
       </c>
@@ -2583,8 +2635,8 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="22"/>
-      <c r="B32" s="21" t="s">
+      <c r="A32" s="24"/>
+      <c r="B32" s="23" t="s">
         <v>126</v>
       </c>
       <c r="C32" s="7" t="s">
@@ -2613,8 +2665,8 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
+      <c r="A33" s="24"/>
+      <c r="B33" s="24"/>
       <c r="C33" s="7" t="s">
         <v>130</v>
       </c>
@@ -2641,8 +2693,8 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A34" s="22"/>
-      <c r="B34" s="22"/>
+      <c r="A34" s="24"/>
+      <c r="B34" s="24"/>
       <c r="C34" s="7" t="s">
         <v>134</v>
       </c>
@@ -2667,8 +2719,8 @@
       <c r="J34" s="7"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A35" s="22"/>
-      <c r="B35" s="23"/>
+      <c r="A35" s="24"/>
+      <c r="B35" s="25"/>
       <c r="C35" s="7" t="s">
         <v>136</v>
       </c>
@@ -2695,8 +2747,8 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A36" s="22"/>
-      <c r="B36" s="21" t="s">
+      <c r="A36" s="24"/>
+      <c r="B36" s="23" t="s">
         <v>139</v>
       </c>
       <c r="C36" s="7" t="s">
@@ -2725,8 +2777,8 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A37" s="22"/>
-      <c r="B37" s="23"/>
+      <c r="A37" s="24"/>
+      <c r="B37" s="25"/>
       <c r="C37" s="7" t="s">
         <v>143</v>
       </c>
@@ -2753,8 +2805,8 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A38" s="22"/>
-      <c r="B38" s="26" t="s">
+      <c r="A38" s="24"/>
+      <c r="B38" s="28" t="s">
         <v>146</v>
       </c>
       <c r="C38" s="7" t="s">
@@ -2783,8 +2835,8 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
+      <c r="A39" s="24"/>
+      <c r="B39" s="24"/>
       <c r="C39" s="7" t="s">
         <v>151</v>
       </c>
@@ -2811,12 +2863,12 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
+      <c r="A40" s="24"/>
+      <c r="B40" s="24"/>
       <c r="C40" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="D40" s="34" t="s">
+      <c r="D40" s="22" t="s">
         <v>156</v>
       </c>
       <c r="E40" s="10" t="s">
@@ -2831,7 +2883,7 @@
       <c r="H40" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="I40" s="33" t="s">
+      <c r="I40" s="21" t="s">
         <v>56</v>
       </c>
       <c r="J40" s="7" t="s">
@@ -2839,8 +2891,8 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A41" s="22"/>
-      <c r="B41" s="22"/>
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
       <c r="C41" s="7" t="s">
         <v>160</v>
       </c>
@@ -2859,7 +2911,7 @@
       <c r="H41" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="I41" s="33" t="s">
+      <c r="I41" s="21" t="s">
         <v>56</v>
       </c>
       <c r="J41" s="7" t="s">
@@ -2867,8 +2919,8 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A42" s="22"/>
-      <c r="B42" s="22"/>
+      <c r="A42" s="24"/>
+      <c r="B42" s="24"/>
       <c r="C42" s="7" t="s">
         <v>165</v>
       </c>
@@ -2895,8 +2947,8 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A43" s="23"/>
-      <c r="B43" s="23"/>
+      <c r="A43" s="25"/>
+      <c r="B43" s="25"/>
       <c r="C43" s="7" t="s">
         <v>169</v>
       </c>
@@ -2965,18 +3017,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
       <c r="K1" s="14"/>
       <c r="L1" s="14"/>
       <c r="M1" s="14"/>
@@ -3074,10 +3126,10 @@
       <c r="AA3" s="5"/>
     </row>
     <row r="4" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="30" t="s">
         <v>75</v>
       </c>
       <c r="C4" s="7" t="s">
@@ -3106,8 +3158,8 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
       <c r="C5" s="7" t="s">
         <v>177</v>
       </c>
@@ -3134,8 +3186,8 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="22"/>
-      <c r="B6" s="22"/>
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="7" t="s">
         <v>180</v>
       </c>
@@ -3162,8 +3214,8 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="22"/>
-      <c r="B7" s="23"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="25"/>
       <c r="C7" s="7" t="s">
         <v>182</v>
       </c>
@@ -3207,8 +3259,8 @@
       <c r="AA7" s="16"/>
     </row>
     <row r="8" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="22"/>
-      <c r="B8" s="28" t="s">
+      <c r="A8" s="24"/>
+      <c r="B8" s="30" t="s">
         <v>108</v>
       </c>
       <c r="C8" s="7" t="s">
@@ -3254,8 +3306,8 @@
       <c r="AA8" s="16"/>
     </row>
     <row r="9" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A9" s="22"/>
-      <c r="B9" s="22"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="7" t="s">
         <v>189</v>
       </c>
@@ -3299,8 +3351,8 @@
       <c r="AA9" s="16"/>
     </row>
     <row r="10" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
       <c r="C10" s="7" t="s">
         <v>193</v>
       </c>
@@ -3344,8 +3396,8 @@
       <c r="AA10" s="16"/>
     </row>
     <row r="11" spans="1:27" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="22"/>
-      <c r="B11" s="23"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="25"/>
       <c r="C11" s="7" t="s">
         <v>197</v>
       </c>
@@ -3389,8 +3441,8 @@
       <c r="AA11" s="16"/>
     </row>
     <row r="12" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A12" s="22"/>
-      <c r="B12" s="27" t="s">
+      <c r="A12" s="24"/>
+      <c r="B12" s="29" t="s">
         <v>202</v>
       </c>
       <c r="C12" s="7" t="s">
@@ -3436,15 +3488,15 @@
       <c r="AA12" s="16"/>
     </row>
     <row r="13" spans="1:27" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="22"/>
-      <c r="B13" s="22"/>
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
       <c r="C13" s="7" t="s">
         <v>52</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="33" t="s">
         <v>208</v>
       </c>
       <c r="F13" s="10" t="s">
@@ -3481,15 +3533,15 @@
       <c r="AA13" s="16"/>
     </row>
     <row r="14" spans="1:27" ht="51" x14ac:dyDescent="0.2">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
+      <c r="A14" s="24"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="7" t="s">
         <v>57</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="E14" s="23"/>
+      <c r="E14" s="25"/>
       <c r="F14" s="10" t="s">
         <v>15</v>
       </c>
@@ -3524,8 +3576,8 @@
       <c r="AA14" s="16"/>
     </row>
     <row r="15" spans="1:27" ht="51" x14ac:dyDescent="0.2">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="24"/>
       <c r="C15" s="7" t="s">
         <v>61</v>
       </c>
@@ -3569,8 +3621,8 @@
       <c r="AA15" s="16"/>
     </row>
     <row r="16" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A16" s="22"/>
-      <c r="B16" s="28" t="s">
+      <c r="A16" s="24"/>
+      <c r="B16" s="30" t="s">
         <v>218</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -3616,8 +3668,8 @@
       <c r="AA16" s="16"/>
     </row>
     <row r="17" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="7" t="s">
         <v>68</v>
       </c>
@@ -3661,8 +3713,8 @@
       <c r="AA17" s="16"/>
     </row>
     <row r="18" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="7" t="s">
         <v>72</v>
       </c>
@@ -3706,8 +3758,8 @@
       <c r="AA18" s="16"/>
     </row>
     <row r="19" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="22"/>
-      <c r="B19" s="22"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
       <c r="C19" s="7" t="s">
         <v>76</v>
       </c>
@@ -3751,8 +3803,8 @@
       <c r="AA19" s="16"/>
     </row>
     <row r="20" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
+      <c r="A20" s="24"/>
+      <c r="B20" s="24"/>
       <c r="C20" s="7" t="s">
         <v>79</v>
       </c>
@@ -3796,8 +3848,8 @@
       <c r="AA20" s="16"/>
     </row>
     <row r="21" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="22"/>
-      <c r="B21" s="23"/>
+      <c r="A21" s="24"/>
+      <c r="B21" s="25"/>
       <c r="C21" s="7" t="s">
         <v>84</v>
       </c>
@@ -3839,8 +3891,8 @@
       <c r="AA21" s="16"/>
     </row>
     <row r="22" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A22" s="22"/>
-      <c r="B22" s="27" t="s">
+      <c r="A22" s="24"/>
+      <c r="B22" s="29" t="s">
         <v>146</v>
       </c>
       <c r="C22" s="7" t="s">
@@ -3886,8 +3938,8 @@
       <c r="AA22" s="16"/>
     </row>
     <row r="23" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
+      <c r="A23" s="24"/>
+      <c r="B23" s="24"/>
       <c r="C23" s="7" t="s">
         <v>91</v>
       </c>
@@ -3931,8 +3983,8 @@
       <c r="AA23" s="16"/>
     </row>
     <row r="24" spans="1:27" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
       <c r="C24" s="7" t="s">
         <v>95</v>
       </c>
@@ -3976,8 +4028,8 @@
       <c r="AA24" s="16"/>
     </row>
     <row r="25" spans="1:27" ht="51" x14ac:dyDescent="0.2">
-      <c r="A25" s="22"/>
-      <c r="B25" s="22"/>
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
       <c r="C25" s="7" t="s">
         <v>99</v>
       </c>
@@ -4021,8 +4073,8 @@
       <c r="AA25" s="16"/>
     </row>
     <row r="26" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
       <c r="C26" s="7" t="s">
         <v>103</v>
       </c>
@@ -4066,8 +4118,8 @@
       <c r="AA26" s="16"/>
     </row>
     <row r="27" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="22"/>
-      <c r="B27" s="23"/>
+      <c r="A27" s="24"/>
+      <c r="B27" s="25"/>
       <c r="C27" s="7" t="s">
         <v>109</v>
       </c>
@@ -4111,8 +4163,8 @@
       <c r="AA27" s="16"/>
     </row>
     <row r="28" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="22"/>
-      <c r="B28" s="28" t="s">
+      <c r="A28" s="24"/>
+      <c r="B28" s="30" t="s">
         <v>232</v>
       </c>
       <c r="C28" s="7" t="s">
@@ -4158,8 +4210,8 @@
       <c r="AA28" s="16"/>
     </row>
     <row r="29" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
       <c r="C29" s="7" t="s">
         <v>115</v>
       </c>
@@ -4203,8 +4255,8 @@
       <c r="AA29" s="16"/>
     </row>
     <row r="30" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="22"/>
-      <c r="B30" s="23"/>
+      <c r="A30" s="24"/>
+      <c r="B30" s="25"/>
       <c r="C30" s="7" t="s">
         <v>119</v>
       </c>
@@ -4248,8 +4300,8 @@
       <c r="AA30" s="16"/>
     </row>
     <row r="31" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="22"/>
-      <c r="B31" s="28" t="s">
+      <c r="A31" s="24"/>
+      <c r="B31" s="30" t="s">
         <v>245</v>
       </c>
       <c r="C31" s="7" t="s">
@@ -4295,8 +4347,8 @@
       <c r="AA31" s="16"/>
     </row>
     <row r="32" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="23"/>
-      <c r="B32" s="23"/>
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
       <c r="C32" s="7" t="s">
         <v>127</v>
       </c>
@@ -4350,14 +4402,14 @@
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="14" spans="16:21" x14ac:dyDescent="0.2">
-      <c r="P14" s="32" t="s">
+      <c r="P14" s="34" t="s">
         <v>251</v>
       </c>
-      <c r="Q14" s="32"/>
-      <c r="R14" s="32"/>
-      <c r="S14" s="32"/>
-      <c r="T14" s="32"/>
-      <c r="U14" s="32"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="34"/>
+      <c r="S14" s="34"/>
+      <c r="T14" s="34"/>
+      <c r="U14" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4395,9 +4447,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2AF56C-CEFE-412D-AAFB-5CEF6AF46D75}">
-  <dimension ref="A1"/>
+  <dimension ref="M4"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="4" spans="13:13" x14ac:dyDescent="0.2">
+      <c r="M4" s="20" t="s">
+        <v>253</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="M4" r:id="rId1" xr:uid="{B00154F1-3CF0-4A20-AA19-B2D96AFE5BA4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>